--- a/tools/_out/orfs_gen_20261020/out/DesignTable_FS6505C_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/DesignTable_FS6505C_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB3"/>
+  <dimension ref="A1:BA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,160 +524,155 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>FSWB_CSANG@DRIVE</t>
+          <t>FSWB_MINR@DRIVE</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>FSWB_MINR@DRIVE</t>
+          <t>FSWB_THDL@DRIVE</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>FSWB_THDL@DRIVE</t>
+          <t>FSWB_RELANG@DRIVE</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>FSWB_RELANG@DRIVE</t>
+          <t>FSWB_RELR@DRIVE</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>FSWB_RELR@DRIVE</t>
+          <t>FSWB_STEMR@DRIVE</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>FSWB_STEMR@DRIVE</t>
+          <t>FSWB_HEADL@DRIVE</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>FSWB_HEADL@DRIVE</t>
+          <t>HELIXDIA@HELIXSK_B</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>HELIXDIA@HELIXSK_B</t>
+          <t>HEIGHT@HELIX_B</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>HEIGHT@HELIX_B</t>
+          <t>PITCH@HELIX_B</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>PITCH@HELIX_B</t>
+          <t>PROF_R@THDPROF_B</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>PROF_R@THDPROF_B</t>
+          <t>APEXR@THDPROF_B</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>APEXR@THDPROF_B</t>
+          <t>FSWB_CBR@DRIVE</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>FSWB_CBR@DRIVE</t>
+          <t>FSWB_CBD@DRIVE</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>FSWB_CBD@DRIVE</t>
+          <t>PROF_AX@THDPROF_B</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>PROF_AX@THDPROF_B</t>
+          <t>DA@BORE_A</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>DA@BORE_A</t>
+          <t>DEPTH@BORECUT_A</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>DEPTH@BORECUT_A</t>
+          <t>DB@BORE_B</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>DB@BORE_B</t>
+          <t>DEPTH@BORECUT_B</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>DEPTH@BORECUT_B</t>
+          <t>START@BORECUT_B</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>START@BORECUT_B</t>
+          <t>DEPTH@HEXCUT</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>DEPTH@HEXCUT</t>
+          <t>NUTHEX@NUTHEX</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>NUTHEX@NUTHEX</t>
+          <t>DEPTH@NUTCUT</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>DEPTH@NUTCUT</t>
+          <t>$PRP@PartNo</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>$PRP@PartNo</t>
+          <t>$PRP@Description</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>$PRP@Description</t>
+          <t>$PRP@GeometryRoot</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>$PRP@GeometryRoot</t>
+          <t>$PRP@EndA_Thread</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>$PRP@EndA_Thread</t>
+          <t>$PRP@EndB_Thread</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>$PRP@EndB_Thread</t>
+          <t>$PRP@DataStatus</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>$PRP@DataStatus</t>
+          <t>$PRP@AxialSource</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>$PRP@AxialSource</t>
+          <t>$COMMENT</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
-        <is>
-          <t>$COMMENT</t>
-        </is>
-      </c>
-      <c r="BB1" t="inlineStr">
         <is>
           <t>$PRP@OMiSKU</t>
         </is>
@@ -753,115 +748,112 @@
         <v>0.571</v>
       </c>
       <c r="W2" t="n">
-        <v>60</v>
+        <v>0.54864</v>
       </c>
       <c r="X2" t="n">
+        <v>0.45364</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.09728</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.5356</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AF2" t="n">
         <v>0.54864</v>
       </c>
-      <c r="Y2" t="n">
-        <v>0.45364</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.5485</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.256</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.09728</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.5356</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.08333</v>
-      </c>
       <c r="AG2" t="n">
-        <v>0.54864</v>
+        <v>0.59375</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.59375</v>
+        <v>0.604</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.604</v>
+        <v>0.05</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.05</v>
+        <v>3.071</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.071</v>
+        <v>0.72</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.72</v>
+        <v>1.065</v>
       </c>
       <c r="AM2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.455</v>
+      </c>
+      <c r="AO2" t="n">
         <v>1.065</v>
       </c>
-      <c r="AN2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1.455</v>
-      </c>
       <c r="AP2" t="n">
-        <v>1.065</v>
+        <v>1.38</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.38</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AS2" t="n">
         <v>0.599</v>
       </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>FS6505-12-12</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>FS6505-12-12</t>
+          <t>ORFS Swivel Connector (female face-seal swivel x male pipe) - swivel nut mouth counterbored (-10 up), 3/4-14 NPTF x 1 3/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>ORFS Swivel Connector (female face-seal swivel x male pipe) - swivel nut mouth counterbored (-10 up), 3/4-14 NPTF x 1 3/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>FS6505C</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>FS6505C</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF</t>
+          <t>1 3/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1 3/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>Air-Way FF6505 (s485, double-pass 2026-10-15, parts.air-way.com/api/series/485, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6505-12-12 (ORFS-p006-t04) | MODEL: L16 pipe tip -&gt; seal face, body hex S1, nut S, bores D2 (pipe side) / D19 (swivel): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to the pipe tip) = L16 + the measured seal -&gt; nut face distance SEAL of the swivel; male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 6505); bore step at the body-hex mid-plane (ASSUMPTION, as 6505); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>Air-Way FF6505 (s485, double-pass 2026-10-15, parts.air-way.com/api/series/485, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6505-12-12 (ORFS-p006-t04) | MODEL: L16 pipe tip -&gt; seal face, body hex S1, nut S, bores D2 (pipe side) / D19 (swivel): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to the pipe tip) = L16 + the measured seal -&gt; nut face distance SEAL of the swivel; male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 6505); bore step at the body-hex mid-plane (ASSUMPTION, as 6505); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
+          <t>Air-Way FF6505 (built to Air-Way); Brennan p6 DIFFERS (up to 0.130 in): overall length L16=2.50 vs Brennan L LGTH=2.370; body hex S1=1.13 vs Brennan H HEX=1.250 | OMi parts file row 5610 (no dimensions)</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
-        <is>
-          <t>Air-Way FF6505 (built to Air-Way); Brennan p6 DIFFERS (up to 0.130 in): overall length L16=2.50 vs Brennan L LGTH=2.370; body hex S1=1.13 vs Brennan H HEX=1.250 | OMi parts file row 5610 (no dimensions)</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
         <is>
           <t>FS6505-12-12</t>
         </is>
@@ -937,115 +929,112 @@
         <v>0.583</v>
       </c>
       <c r="W3" t="n">
-        <v>60</v>
+        <v>0.67364</v>
       </c>
       <c r="X3" t="n">
+        <v>0.46574</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.6735</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.34728</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.5477</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AF3" t="n">
         <v>0.67364</v>
       </c>
-      <c r="Y3" t="n">
-        <v>0.46574</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.6735</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.34728</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.5477</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.08333</v>
-      </c>
       <c r="AG3" t="n">
-        <v>0.67364</v>
+        <v>0.71875</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.71875</v>
+        <v>0.729</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.729</v>
+        <v>0.05</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.05</v>
+        <v>3.453</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.453</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.305</v>
       </c>
       <c r="AM3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.585</v>
+      </c>
+      <c r="AO3" t="n">
         <v>1.305</v>
       </c>
-      <c r="AN3" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1.585</v>
-      </c>
       <c r="AP3" t="n">
-        <v>1.305</v>
+        <v>1.67</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AS3" t="n">
         <v>0.65</v>
       </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>FS6505-16-16</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>FS6505-16-16</t>
+          <t>ORFS Swivel Connector (female face-seal swivel x male pipe) - swivel nut mouth counterbored (-10 up), 1-11 1/2 NPTF x 1 7/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>ORFS Swivel Connector (female face-seal swivel x male pipe) - swivel nut mouth counterbored (-10 up), 1-11 1/2 NPTF x 1 7/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>FS6505C</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>FS6505C</t>
+          <t>1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>1 7/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1 7/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>Air-Way FF6505 (s485, double-pass 2026-10-15, parts.air-way.com/api/series/485, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6505-16-16 (ORFS-p006-t04) | MODEL: L16 pipe tip -&gt; seal face, body hex S1, nut S, bores D2 (pipe side) / D19 (swivel): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to the pipe tip) = L16 + the measured seal -&gt; nut face distance SEAL of the swivel; male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 6505); bore step at the body-hex mid-plane (ASSUMPTION, as 6505); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Air-Way FF6505 (s485, double-pass 2026-10-15, parts.air-way.com/api/series/485, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6505-16-16 (ORFS-p006-t04) | MODEL: L16 pipe tip -&gt; seal face, body hex S1, nut S, bores D2 (pipe side) / D19 (swivel): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to the pipe tip) = L16 + the measured seal -&gt; nut face distance SEAL of the swivel; male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 6505); bore step at the body-hex mid-plane (ASSUMPTION, as 6505); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
+          <t>Air-Way FF6505 (built to Air-Way); Brennan p6 DIFFERS (&lt;= 0.02 in): overall length L16=2.87 vs Brennan L LGTH=2.880; nut hex S=1.61 vs Brennan C HEX=1.625; swivel-end bore d19=0.79 vs Brennan B HOLE=0.783 | OMi parts file row 5611 (no dimensions) | swivel nut hex SHEX printed 1.61 - not the FF318 nut S 1.63 of -16: built with FF318 S 1.63 (Q-FS-NUT)</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
-        <is>
-          <t>Air-Way FF6505 (built to Air-Way); Brennan p6 DIFFERS (&lt;= 0.02 in): overall length L16=2.87 vs Brennan L LGTH=2.880; nut hex S=1.61 vs Brennan C HEX=1.625; swivel-end bore d19=0.79 vs Brennan B HOLE=0.783 | OMi parts file row 5611 (no dimensions) | swivel nut hex SHEX printed 1.61 - not the FF318 nut S 1.63 of -16: built with FF318 S 1.63 (Q-FS-NUT)</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
         <is>
           <t>FS6505-16-16</t>
         </is>
